--- a/planilha investimentos.xlsx
+++ b/planilha investimentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63984781760831fe/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A3C4A6E1-E17D-43BD-890F-BE3F3CE81715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B86B010E-D226-4812-8B84-2F5F253CDD98}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{A3C4A6E1-E17D-43BD-890F-BE3F3CE81715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B551FF4E-0181-46B2-BE0E-D8FB0ADC0EA9}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11664" windowHeight="12336" activeTab="1" xr2:uid="{4D3280B7-5F17-4E91-A141-6930EF350F7D}"/>
+    <workbookView xWindow="2220" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{4D3280B7-5F17-4E91-A141-6930EF350F7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -723,7 +723,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -768,11 +768,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -783,7 +783,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -795,7 +794,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -812,7 +810,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -830,6 +828,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="40% - Ênfase3" xfId="5" builtinId="39"/>
@@ -919,6 +918,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -934,6 +938,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -949,6 +958,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -964,6 +978,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -979,6 +998,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -996,6 +1020,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-9F9F-4358-9A69-F24C51BBBF12}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2148,7 +2177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DA51E0-14F7-4A90-8A07-F7078AD9C00E}">
-  <dimension ref="A9:H43"/>
+  <dimension ref="A9:H44"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -2266,7 +2295,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="49">
+      <c r="A24" s="47">
         <v>2</v>
       </c>
       <c r="B24" s="29" t="s">
@@ -2282,7 +2311,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49">
+      <c r="A25" s="47">
         <v>5</v>
       </c>
       <c r="B25" s="29" t="s">
@@ -2298,7 +2327,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="49">
+      <c r="A26" s="47">
         <v>10</v>
       </c>
       <c r="B26" s="29" t="s">
@@ -2314,7 +2343,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="49">
+      <c r="A27" s="47">
         <v>20</v>
       </c>
       <c r="B27" s="29" t="s">
@@ -2330,7 +2359,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="49">
+      <c r="A28" s="47">
         <v>30</v>
       </c>
       <c r="B28" s="30" t="s">
@@ -2340,7 +2369,7 @@
         <f>FV(taxa_mensal,$A28*12,aporte)*-1</f>
         <v>2166952.4051583759</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="51">
         <f>C28*$C$12</f>
         <v>21669.524051583758</v>
       </c>
@@ -2352,46 +2381,46 @@
       <c r="C32" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="33">
         <f>aporte</f>
         <v>500</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <f>aporte</f>
         <v>500</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="50">
+      <c r="C34" s="48">
         <v>0.3</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="49">
         <f>salario*C34</f>
         <v>1500</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="34" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2399,16 +2428,16 @@
       <c r="B37" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="48">
+      <c r="C37" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B37,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.3</v>
       </c>
-      <c r="D37" s="36">
-        <f>aporte*$C37</f>
+      <c r="D37" s="35">
+        <f t="shared" ref="D37:D42" si="0">aporte*$C37</f>
         <v>150</v>
       </c>
-      <c r="E37" s="52">
-        <f>$D$34*$C37</f>
+      <c r="E37" s="50">
+        <f t="shared" ref="E37:E42" si="1">$D$34*$C37</f>
         <v>450</v>
       </c>
     </row>
@@ -2416,16 +2445,16 @@
       <c r="B38" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B38,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.5</v>
       </c>
-      <c r="D38" s="36">
-        <f>aporte*$C38</f>
+      <c r="D38" s="35">
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="E38" s="52">
-        <f>$D$34*$C38</f>
+      <c r="E38" s="50">
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
     </row>
@@ -2433,16 +2462,16 @@
       <c r="B39" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B39,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D39" s="36">
-        <f>aporte*$C39</f>
+      <c r="D39" s="35">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="E39" s="52">
-        <f>$D$34*$C39</f>
+      <c r="E39" s="50">
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -2450,16 +2479,16 @@
       <c r="B40" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B40,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D40" s="36">
-        <f>aporte*$C40</f>
+      <c r="D40" s="35">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="E40" s="52">
-        <f>$D$34*$C40</f>
+      <c r="E40" s="50">
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -2467,16 +2496,16 @@
       <c r="B41" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B41,Planilha2!$A:$D,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="36">
-        <f>aporte*$C41</f>
+      <c r="D41" s="35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E41" s="52">
-        <f>$D$34*$C41</f>
+      <c r="E41" s="50">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2484,32 +2513,35 @@
       <c r="B42" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="46">
         <f>VLOOKUP($C$32&amp;"-"&amp;B42,Planilha2!$A:$D,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="36">
-        <f>aporte*$C42</f>
+      <c r="D42" s="35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E42" s="52">
-        <f>$D$34*$C42</f>
+      <c r="E42" s="50">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="47">
+      <c r="C43" s="34"/>
+      <c r="D43" s="45">
         <f>D37+D38+D39+D40+D41+D42</f>
         <v>500</v>
       </c>
-      <c r="E43" s="61" t="e">
-        <f>redinemtno_carteira</f>
-        <v>#NAME?</v>
-      </c>
+      <c r="E43" s="59">
+        <f>E37+E38+E39+E40+E41+E42</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E44" s="60"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2535,21 +2567,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="57" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54" t="str">
+      <c r="A3" s="52" t="str">
         <f>B3&amp;"-"&amp;C3</f>
         <v>Conservador-PAPEL</v>
       </c>
@@ -2559,7 +2591,7 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="36">
         <v>0.3</v>
       </c>
       <c r="H3" t="s">
@@ -2567,7 +2599,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="str">
+      <c r="A4" s="52" t="str">
         <f>B4&amp;"-"&amp;C4</f>
         <v>Conservador-TIJOLO</v>
       </c>
@@ -2577,19 +2609,19 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="36">
         <v>0.5</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="44">
         <f>VLOOKUP(G4,$A:$D,4,)</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="str">
+      <c r="A5" s="52" t="str">
         <f>B5&amp;"-"&amp;C5</f>
         <v>Conservador-HÍBRIDOS</v>
       </c>
@@ -2599,13 +2631,13 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="36">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="str">
-        <f t="shared" ref="A6:A8" si="0">B6&amp;"-"&amp;C6</f>
+      <c r="A6" s="52" t="str">
+        <f t="shared" ref="A6" si="0">B6&amp;"-"&amp;C6</f>
         <v>Conservador-FOFs</v>
       </c>
       <c r="B6" t="s">
@@ -2614,12 +2646,12 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="36">
         <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="str">
+      <c r="A7" s="52" t="str">
         <f>B7&amp;"-"&amp;C7</f>
         <v>Conservador-DESENVOLVIMENTO</v>
       </c>
@@ -2629,13 +2661,13 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="36">
         <v>0</v>
       </c>
       <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="54" t="str">
+      <c r="A8" s="52" t="str">
         <f>B8&amp;"-"&amp;C8</f>
         <v>Conservador-HOTELARIAS</v>
       </c>
@@ -2645,102 +2677,102 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="str">
+      <c r="A9" s="53" t="str">
         <f t="shared" ref="A9:A20" si="1">B9&amp;"-"&amp;C9</f>
         <v>Moderado-PAPEL</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="39">
         <v>0.32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="56" t="str">
+      <c r="A10" s="54" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-TIJOLO</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="40">
         <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="56" t="str">
+      <c r="A11" s="54" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-HÍBRIDOS</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="40">
         <v>0.08</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="56" t="str">
+      <c r="A12" s="54" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-FOFs</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="40">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="56" t="str">
+      <c r="A13" s="54" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-DESENVOLVIMENTO</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="40">
         <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="57" t="str">
+      <c r="A14" s="55" t="str">
         <f t="shared" si="1"/>
         <v>Moderado-HOTELARIAS</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="41">
         <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="54" t="str">
+      <c r="A15" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-PAPEL</v>
       </c>
@@ -2750,12 +2782,12 @@
       <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="42">
         <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="str">
+      <c r="A16" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-TIJOLO</v>
       </c>
@@ -2765,12 +2797,12 @@
       <c r="C16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="42">
         <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="54" t="str">
+      <c r="A17" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-HÍBRIDOS</v>
       </c>
@@ -2780,12 +2812,12 @@
       <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="42">
         <v>0.05</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="54" t="str">
+      <c r="A18" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-FOFs</v>
       </c>
@@ -2795,12 +2827,12 @@
       <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="42">
         <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="54" t="str">
+      <c r="A19" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-DESENVOLVIMENTO</v>
       </c>
@@ -2810,12 +2842,12 @@
       <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="42">
         <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="54" t="str">
+      <c r="A20" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Agressivo-HOTELARIAS</v>
       </c>
@@ -2825,7 +2857,7 @@
       <c r="C20" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="42">
         <v>0.1</v>
       </c>
     </row>
